--- a/AAII_Financials/Quarterly/FLMNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FLMNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="92">
   <si>
     <t>FLMNY</t>
   </si>
@@ -656,73 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +771,17 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,8 +818,17 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +865,17 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +890,11 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +931,17 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +978,17 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +1025,17 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1072,17 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,8 +1094,11 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1054,8 +1135,17 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,8 +1182,17 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1207,11 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1146,8 +1248,17 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1184,8 +1295,17 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,8 +1342,17 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1260,8 +1389,17 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1436,17 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1483,17 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1374,8 +1530,17 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1412,8 +1577,17 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1624,17 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1671,17 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1718,17 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1765,17 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,8 +1812,17 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1640,8 +1859,17 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,8 +1906,17 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1716,51 +1953,69 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +2030,11 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,350 +2049,434 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>4</v>
+      <c r="D41" s="3">
+        <v>302600</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F41" s="3">
+        <v>261200</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3">
+        <v>226900</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>97600</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>362200</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>65100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>112600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>121900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K42" s="3">
         <v>4500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>25300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>72600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>86000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="Q42" s="3">
         <v>105400</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>244600</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F43" s="3">
-        <v>156700</v>
+        <v>226100</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H43" s="3">
+        <v>194000</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
+        <v>202700</v>
+      </c>
+      <c r="K43" s="3">
         <v>168900</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>172800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O43" s="3">
         <v>138200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>127400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>119000</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
+      <c r="D44" s="3">
+        <v>272000</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F44" s="3">
-        <v>268500</v>
+        <v>260900</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="3">
+        <v>300300</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
+        <v>235200</v>
+      </c>
+      <c r="K44" s="3">
         <v>257200</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>248400</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3">
         <v>228800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>219400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>195800</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>43300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F45" s="3">
-        <v>34500</v>
+        <v>46000</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H45" s="3">
+        <v>39600</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K45" s="3">
         <v>42100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>52500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>40200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>43700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>48600</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4</v>
+      <c r="D46" s="3">
+        <v>867000</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F46" s="3">
-        <v>564900</v>
+        <v>794200</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H46" s="3">
+        <v>766000</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
+        <v>577700</v>
+      </c>
+      <c r="K46" s="3">
         <v>834900</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>564200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>592400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>598400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>523600</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>5400</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F47" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>5000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>10900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>13700</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>11900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>23100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>25900</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
+      <c r="D48" s="3">
+        <v>1182200</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F48" s="3">
+        <v>1224500</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1135300</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>1036400</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>953200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>995500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>889800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>895600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>885000</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>813000</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>794200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>806400</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>761300</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>542600</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>573300</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>457700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>423200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>411400</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2513,17 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2560,64 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>23100</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F52" s="3">
+        <v>24200</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>13600</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>21700</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>13800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>22200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>22300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2654,64 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>4</v>
+      <c r="D54" s="3">
+        <v>2965200</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F54" s="3">
-        <v>2452600</v>
+        <v>2917900</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H54" s="3">
+        <v>2804300</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
+        <v>2465400</v>
+      </c>
+      <c r="K54" s="3">
         <v>2392400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>2231800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>1995700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>1984000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>1888200</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2726,11 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,236 +2745,293 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>112400</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F57" s="3">
+        <v>120400</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
+        <v>113200</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>93400</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>101000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>101900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>113600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>108800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>91100</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>122600</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>115300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>131400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>421000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>113400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>189100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>119300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>112100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>129400</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>407200</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F59" s="3">
+        <v>348400</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
+        <v>419300</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>280400</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>476400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>329600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>145900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>154200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>642200</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F60" s="3">
+        <v>666200</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
+        <v>663800</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>876600</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>764500</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>692700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>455600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>473000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>898800</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>483700</v>
+        <v>917700</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>516800</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>483400</v>
+      </c>
+      <c r="K61" s="3">
         <v>442600</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>465500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>387200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>403700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>411000</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>88200</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F62" s="3">
-        <v>60000</v>
+        <v>49800</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H62" s="3">
+        <v>421500</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
+        <v>46800</v>
+      </c>
+      <c r="K62" s="3">
         <v>61900</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>48300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>98500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>95100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>84800</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +3068,17 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +3115,17 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +3162,64 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
+      <c r="D66" s="3">
+        <v>1697000</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F66" s="3">
-        <v>1507200</v>
+        <v>1745900</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H66" s="3">
+        <v>1662800</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1509900</v>
+      </c>
+      <c r="K66" s="3">
         <v>1324000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>1291600</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>986800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>1012800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>976300</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3234,11 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3275,17 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3322,17 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3369,17 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3416,64 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
+      <c r="D72" s="3">
+        <v>1045900</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F72" s="3">
-        <v>705100</v>
+        <v>948100</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H72" s="3">
+        <v>921300</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
+        <v>715200</v>
+      </c>
+      <c r="K72" s="3">
         <v>832300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>640100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>725500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>691200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>635000</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3510,17 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3557,17 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3604,64 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1253300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1132000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1152700</v>
+      </c>
+      <c r="G76" s="3">
         <v>1123400</v>
       </c>
-      <c r="E76" s="3">
-        <v>971800</v>
-      </c>
-      <c r="F76" s="3">
-        <v>930900</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H76" s="3">
+        <v>1124500</v>
+      </c>
+      <c r="I76" s="3">
+        <v>982400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>941000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1053800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>854500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>875500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>952800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>914300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>856200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,51 +3698,69 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3212,8 +3797,17 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,8 +3822,11 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3245,29 +3842,38 @@
       <c r="G83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>53400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>47600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>34100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>41200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>43700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>46300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3910,17 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3957,17 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +4004,17 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +4051,17 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,8 +4098,17 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3485,17 +4136,26 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
         <v>53900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>103900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,8 +4170,11 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3539,17 +4202,26 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3">
         <v>-22900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-17500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-39000</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4258,17 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,8 +4305,17 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3653,17 +4343,26 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
         <v>-31500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-5000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-85300</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +4377,11 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3710,14 +4412,23 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>1000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4465,17 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4512,17 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,8 +4559,17 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3859,17 +4597,26 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3">
         <v>-32500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-32600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-26800</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3885,29 +4632,38 @@
       <c r="G101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3936,12 +4692,21 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-9900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>66300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-32400</v>
       </c>
     </row>
